--- a/output/pdf_financials_xlsx/PIC.A.xlsx
+++ b/output/pdf_financials_xlsx/PIC.A.xlsx
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>66.16833200000001</v>
+        <v>3.406298</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>22.036125</v>
+        <v>3.523722</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.91239</v>
+        <v>2.690289</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.789547</v>
+        <v>2.376925</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.826419</v>
+        <v>2.688279</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>2.023634</v>
+        <v>2.69611</v>
       </c>
     </row>
     <row r="11">
@@ -674,22 +674,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-54.572626</v>
+        <v>8.189408</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-9.625883</v>
+        <v>8.886520000000001</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5.992331</v>
+        <v>5.214432</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>6.872995</v>
+        <v>6.285617</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>6.615688</v>
+        <v>5.753828</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>6.918435</v>
+        <v>6.245959</v>
       </c>
     </row>
     <row r="12">
@@ -1291,22 +1291,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.713207</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.621501</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.364217</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.387005</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.465368</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.872525</v>
       </c>
     </row>
     <row r="35">
@@ -1341,22 +1341,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.713207</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.621501</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.364217</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.387005</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.465368</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.872525</v>
       </c>
     </row>
     <row r="37">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">

--- a/output/pdf_financials_xlsx/PIC.A.xlsx
+++ b/output/pdf_financials_xlsx/PIC.A.xlsx
@@ -574,22 +574,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2.669348</v>
+        <v>2.688655</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2.67428</v>
+        <v>2.6958</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.91239</v>
+        <v>1.934225</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.789547</v>
+        <v>1.810437</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.826419</v>
+        <v>1.846964</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2.023634</v>
+        <v>2.044034</v>
       </c>
     </row>
     <row r="8">
@@ -9726,7 +9726,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E138" s="5" t="n">
         <v>0.019307</v>
       </c>
@@ -14070,7 +14074,11 @@
           <t>Distributions to Preferred shares</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E241" s="5" t="n">
         <v>-13.966138</v>
       </c>
